--- a/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96081674-B8F6-4DA8-9060-B784F859DDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{894BCE6E-753B-433E-9F8B-453188DE53DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -837,13 +837,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S03aH02,S01aH06,S02aH03,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH05,S04aH08,S04aH06,S01aH02,S04aH04,S02aH02,S04aH02,S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
+    <t>S02aH04,S02aH05,S02aH02,S03aH03,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S01aH04,S01aH07,S02aH07,S04aH03,S04aH02,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S01aH03,S01aH02,S04aH04,S04aH06</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S04aH02,S01aH01,S04aH01,S03aH09,S02aH01,S02aH10,S04aH08,S01aH08,S02aH08,S03aH01,S01aH10,S03aH02,S02aH02,S04aH10,S01aH09,S03aH08,S03aH10,S01aH02</t>
+    <t>S03aH08,S03aH10,S03aH01,S02aH02,S04aH10,S01aH02,S01aH01,S04aH01,S01aH09,S02aH01,S02aH10,S01aH10,S03aH02,S02aH09,S04aH09,S03aH09,S04aH02,S04aH08,S01aH08,S02aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S04aH02,S01aH01,S04aH01,S03aH09,S02aH01,S02aH10,S04aH08,S01aH08,S02aH08,S03aH01,S01aH10,S03aH02,S02aH02,S04aH10,S01aH09,S03aH08,S03aH10,S01aH02</v>
+        <v>S03aH08,S03aH10,S03aH01,S02aH02,S04aH10,S01aH02,S01aH01,S04aH01,S01aH09,S02aH01,S02aH10,S01aH10,S03aH02,S02aH09,S04aH09,S03aH09,S04aH02,S04aH08,S01aH08,S02aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S03aH02,S01aH06,S02aH03,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH05,S04aH08,S04aH06,S01aH02,S04aH04,S02aH02,S04aH02,S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
+        <v>S02aH04,S02aH05,S02aH02,S03aH03,S04aH05,S04aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S01aH06,S02aH03,S01aH04,S01aH07,S02aH07,S04aH03,S04aH02,S03aH04,S02aH06,S03aH05,S03aH08,S04aH07,S03aH02,S01aH03,S01aH02,S04aH04,S04aH06</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1566,7 +1566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAB8D74-7CDC-4B41-B6B9-1AB879751A54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8E3E69-1863-484A-8D9D-03096838DC7D}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1704,7 +1704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2733E67-DF70-4181-959E-BEF91D6CA745}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F20A56-095C-4F34-A156-6E08EA9361B9}">
   <dimension ref="B9:O1370"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40966,7 +40966,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F288D6-4777-49DC-B597-4EEE3CEC0ABA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{328AC251-8F13-4544-8CF3-4A5FF47EE333}">
   <dimension ref="B9:FT86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62257,7 +62257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF005BF-2FD7-4491-906F-3B81451ED7E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75631BDA-2746-4105-BEC8-2BBD13C7EACD}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62847,7 +62847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD268B87-FBB2-4ABB-A807-47494286CEBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7B9B2C-B757-488B-AC4E-DB838622B021}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63754,7 +63754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99AB7A0E-F0EA-4500-816B-EA106C6FEEFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B3C02E-85DB-48C0-874E-C23EBDA821B9}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64221,7 +64221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B0C200-825E-4A6B-A4FE-F178B0D01F40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811C2BE6-B634-40F3-B444-1735EF906ACA}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64295,7 +64295,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.23416666666666663</v>
+        <v>0.23416666666666666</v>
       </c>
       <c r="E14" t="s">
         <v>273</v>
@@ -64407,7 +64407,7 @@
         <v>45</v>
       </c>
       <c r="D22">
-        <v>0.19613333333333335</v>
+        <v>0.1961333333333333</v>
       </c>
       <c r="E22" t="s">
         <v>273</v>
@@ -65023,7 +65023,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.27663333333333334</v>
+        <v>0.27663333333333329</v>
       </c>
       <c r="E66" t="s">
         <v>273</v>
@@ -65079,7 +65079,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.34016666666666667</v>
+        <v>0.34016666666666673</v>
       </c>
       <c r="E70" t="s">
         <v>273</v>
@@ -65359,7 +65359,7 @@
         <v>45</v>
       </c>
       <c r="D90">
-        <v>0.32973333333333332</v>
+        <v>0.32973333333333327</v>
       </c>
       <c r="E90" t="s">
         <v>273</v>
@@ -65415,7 +65415,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.33363333333333328</v>
+        <v>0.33363333333333339</v>
       </c>
       <c r="E94" t="s">
         <v>273</v>
@@ -65639,7 +65639,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.26300000000000001</v>
+        <v>0.26299999999999996</v>
       </c>
       <c r="E110" t="s">
         <v>273</v>
